--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
@@ -564,42 +564,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -609,16 +609,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="Q2" t="n">
         <v>0.31</v>
@@ -632,16 +632,16 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -663,27 +663,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -693,54 +693,54 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0.31</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -762,22 +762,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q4" t="n">
         <v>0.31</v>
@@ -833,13 +833,13 @@
         <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -861,44 +861,44 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>right</t>
@@ -906,12 +906,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
         <v>8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -960,32 +960,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1010,34 +1010,34 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>0.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1089,27 +1089,27 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1120,23 +1120,23 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
         <v>10</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1158,22 +1158,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1208,18 +1208,18 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1229,13 +1229,13 @@
         <v>10</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1257,47 +1257,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,34 +1307,34 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1356,42 +1356,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
         <v>6</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1455,84 +1455,84 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0.4</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>18</v>
+      </c>
+      <c r="W11" t="n">
         <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1653,84 +1653,84 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1752,52 +1752,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1806,30 +1806,30 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S14" t="n">
         <v>14</v>
       </c>
       <c r="T14" t="n">
+        <v>16</v>
+      </c>
+      <c r="U14" t="n">
         <v>15</v>
       </c>
-      <c r="U14" t="n">
-        <v>13</v>
-      </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,22 +1881,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1905,14 +1905,14 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2021,13 +2021,13 @@
         <v>14</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2049,84 +2049,84 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -2148,47 +2148,47 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2247,42 +2247,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -2346,52 +2346,52 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2400,30 +2400,30 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2445,84 +2445,84 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" t="n">
         <v>8</v>
       </c>
-      <c r="U21" t="n">
-        <v>5</v>
-      </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
         <v>10</v>
@@ -2621,7 +2621,7 @@
         <v>14</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2787,19 +2787,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2813,13 +2813,13 @@
         <v>4</v>
       </c>
       <c r="U24" t="n">
+        <v>6</v>
+      </c>
+      <c r="V24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
-        <v>15</v>
-      </c>
       <c r="W24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2891,34 +2891,34 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S25" t="n">
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" t="n">
         <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>7</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -2940,42 +2940,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2985,19 +2985,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3084,19 +3084,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -3107,16 +3107,16 @@
         <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -3138,42 +3138,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3183,16 +3183,16 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="Q28" t="n">
         <v>0.25</v>
@@ -3206,16 +3206,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -3237,27 +3237,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3267,54 +3267,54 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q29" t="n">
         <v>0.25</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S29" t="n">
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U29" t="n">
         <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3386,18 +3386,18 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3407,13 +3407,13 @@
         <v>4</v>
       </c>
       <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="n">
         <v>8</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -3435,42 +3435,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3492,7 +3492,7 @@
         <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3503,16 +3503,16 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -3534,47 +3534,47 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3584,34 +3584,34 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q32" t="n">
         <v>0.42</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S32" t="n">
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -3633,47 +3633,47 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,34 +3683,34 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P33" t="n">
         <v>0.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
         <v>10</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -3732,22 +3732,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3767,22 +3767,22 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3803,13 +3803,13 @@
         <v>10</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3831,84 +3831,84 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>7</v>
+      </c>
+      <c r="V35" t="n">
         <v>2</v>
       </c>
-      <c r="U35" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>15</v>
-      </c>
-      <c r="W35" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3930,42 +3930,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3975,19 +3975,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
         <v>6</v>
       </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="W36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -4029,84 +4029,84 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
         <v>0.33</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U37" t="n">
+        <v>8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>18</v>
+      </c>
+      <c r="W37" t="n">
         <v>5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>14</v>
-      </c>
-      <c r="W37" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -4128,52 +4128,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4182,30 +4182,30 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -4227,42 +4227,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q39" t="n">
         <v>0.27</v>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -4326,52 +4326,52 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>guitar</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4380,30 +4380,30 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
         <v>14</v>
       </c>
       <c r="T40" t="n">
+        <v>16</v>
+      </c>
+      <c r="U40" t="n">
         <v>15</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" t="n">
         <v>13</v>
-      </c>
-      <c r="V40" t="n">
-        <v>12</v>
-      </c>
-      <c r="W40" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -4499,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4549,27 +4549,27 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4595,13 +4595,13 @@
         <v>14</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -4623,42 +4623,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4668,19 +4668,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4691,16 +4691,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -4722,42 +4722,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q44" t="n">
         <v>0.42</v>
@@ -4790,16 +4790,16 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -4821,32 +4821,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4856,22 +4856,22 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -4882,23 +4882,23 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>15</v>
       </c>
       <c r="W45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -4920,57 +4920,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -4981,23 +4981,23 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
+        <v>9</v>
+      </c>
+      <c r="V46" t="n">
         <v>8</v>
       </c>
-      <c r="V46" t="n">
-        <v>5</v>
-      </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -5019,52 +5019,52 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5073,30 +5073,30 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
+        <v>9</v>
+      </c>
+      <c r="U47" t="n">
         <v>8</v>
       </c>
-      <c r="U47" t="n">
-        <v>5</v>
-      </c>
       <c r="V47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W47" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5186,13 +5186,13 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
         <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W48" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5262,19 +5262,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W49" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5366,18 +5366,18 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q50" t="n">
         <v>0.47</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5387,13 +5387,13 @@
         <v>4</v>
       </c>
       <c r="U50" t="n">
+        <v>6</v>
+      </c>
+      <c r="V50" t="n">
+        <v>15</v>
+      </c>
+      <c r="W50" t="n">
         <v>1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>14</v>
-      </c>
-      <c r="W50" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -5415,42 +5415,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -5514,17 +5514,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5554,17 +5554,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -5575,17 +5575,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S52" t="n">
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U52" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V52" t="n">
         <v>15</v>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5628,17 +5628,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5658,19 +5658,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
         <v>0.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5681,16 +5681,16 @@
         <v>14</v>
       </c>
       <c r="T53" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U53" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V53" t="n">
         <v>14</v>
       </c>
       <c r="W53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -5712,42 +5712,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="Q54" t="n">
         <v>0.25</v>
@@ -5780,16 +5780,16 @@
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U54" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -5811,27 +5811,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>right</t>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5879,16 +5879,16 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U55" t="n">
         <v>4</v>
       </c>
       <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -5910,22 +5910,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5935,43 +5935,43 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q56" t="n">
         <v>0.36</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5981,13 +5981,13 @@
         <v>4</v>
       </c>
       <c r="U56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -6009,52 +6009,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6063,30 +6063,30 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q57" t="n">
         <v>0.36</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S57" t="n">
         <v>5</v>
       </c>
       <c r="T57" t="n">
+        <v>9</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
         <v>8</v>
       </c>
-      <c r="U57" t="n">
-        <v>3</v>
-      </c>
-      <c r="V57" t="n">
-        <v>9</v>
-      </c>
       <c r="W57" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -6108,32 +6108,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6143,22 +6143,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -6169,23 +6169,23 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V58" t="n">
         <v>10</v>
       </c>
       <c r="W58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -6207,27 +6207,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6257,25 +6257,25 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q59" t="n">
         <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U59" t="n">
         <v>10</v>
@@ -6284,7 +6284,7 @@
         <v>6</v>
       </c>
       <c r="W59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -6306,22 +6306,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6331,22 +6331,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6356,18 +6356,18 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6377,13 +6377,13 @@
         <v>10</v>
       </c>
       <c r="U60" t="n">
+        <v>3</v>
+      </c>
+      <c r="V60" t="n">
         <v>2</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>15</v>
-      </c>
-      <c r="W60" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -6405,32 +6405,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="P61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0.33</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.2</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V61" t="n">
         <v>8</v>
       </c>
       <c r="W61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -6504,47 +6504,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6554,34 +6554,34 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S62" t="n">
         <v>10</v>
       </c>
       <c r="T62" t="n">
+        <v>7</v>
+      </c>
+      <c r="U62" t="n">
         <v>6</v>
       </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W62" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
@@ -6603,47 +6603,47 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6653,34 +6653,34 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>6</v>
+      </c>
+      <c r="U63" t="n">
+        <v>8</v>
+      </c>
+      <c r="V63" t="n">
         <v>1</v>
       </c>
-      <c r="U63" t="n">
-        <v>5</v>
-      </c>
-      <c r="V63" t="n">
-        <v>14</v>
-      </c>
       <c r="W63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -6702,42 +6702,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6747,16 +6747,16 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q64" t="n">
         <v>0.47</v>
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="W64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -6801,84 +6801,84 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P65" t="n">
         <v>0.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S65" t="n">
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -6900,37 +6900,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6957,24 +6957,24 @@
         <v>0.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S66" t="n">
         <v>14</v>
       </c>
       <c r="T66" t="n">
+        <v>16</v>
+      </c>
+      <c r="U66" t="n">
         <v>15</v>
       </c>
-      <c r="U66" t="n">
-        <v>13</v>
-      </c>
       <c r="V66" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="W66" t="n">
         <v>3</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,38 +7029,38 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W67" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7123,22 +7123,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7148,18 +7148,18 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P68" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q68" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.25</v>
-      </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7169,13 +7169,13 @@
         <v>14</v>
       </c>
       <c r="U68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -7197,84 +7197,84 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q69" t="n">
         <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S69" t="n">
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
         <v>3</v>
       </c>
-      <c r="V69" t="n">
-        <v>10</v>
-      </c>
       <c r="W69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -7296,42 +7296,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7341,16 +7341,16 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q70" t="n">
         <v>0.36</v>
@@ -7364,16 +7364,16 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -7395,84 +7395,84 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
@@ -7494,84 +7494,84 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -7593,47 +7593,47 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7643,34 +7643,34 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S73" t="n">
         <v>8</v>
       </c>
       <c r="T73" t="n">
+        <v>9</v>
+      </c>
+      <c r="U73" t="n">
         <v>8</v>
       </c>
-      <c r="U73" t="n">
-        <v>5</v>
-      </c>
       <c r="V73" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W73" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -7692,27 +7692,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7722,54 +7722,54 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S74" t="n">
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U74" t="n">
         <v>10</v>
       </c>
       <c r="V74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,38 +7821,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>4</v>
       </c>
       <c r="V75" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7915,22 +7915,22 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7940,18 +7940,18 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7961,13 +7961,13 @@
         <v>4</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V76" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W76" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -7989,52 +7989,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8043,30 +8043,30 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V77" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -8088,42 +8088,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8133,19 +8133,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8156,16 +8156,16 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U78" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V78" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -8187,52 +8187,52 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8241,30 +8241,30 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S79" t="n">
         <v>14</v>
       </c>
       <c r="T79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U79" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8286,37 +8286,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8340,27 +8340,27 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S80" t="n">
         <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U80" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
         <v>15</v>
@@ -8385,27 +8385,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8430,19 +8430,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -8453,16 +8453,16 @@
         <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U81" t="n">
         <v>4</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -8484,22 +8484,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8509,22 +8509,22 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8534,18 +8534,18 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8555,13 +8555,13 @@
         <v>4</v>
       </c>
       <c r="U82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W82" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -8583,52 +8583,52 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8637,30 +8637,30 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q83" t="n">
         <v>0.36</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S83" t="n">
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W83" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
@@ -8682,42 +8682,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8739,7 +8739,7 @@
         <v>0.75</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>5</v>
+      </c>
+      <c r="V84" t="n">
         <v>3</v>
       </c>
-      <c r="U84" t="n">
-        <v>7</v>
-      </c>
-      <c r="V84" t="n">
-        <v>2</v>
-      </c>
       <c r="W84" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -8781,39 +8781,39 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>hand</t>
@@ -8821,41 +8821,41 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S85" t="n">
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U85" t="n">
         <v>10</v>
       </c>
       <c r="V85" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W85" t="n">
         <v>8</v>
@@ -8880,22 +8880,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8905,43 +8905,43 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8951,13 +8951,13 @@
         <v>10</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W86" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -8979,47 +8979,47 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_13.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9029,34 +9029,34 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="Q87" t="n">
         <v>0.2</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S87" t="n">
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V87" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="W87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -9078,84 +9078,84 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_01.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S88" t="n">
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>7</v>
+      </c>
+      <c r="U88" t="n">
         <v>6</v>
       </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
       <c r="V88" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W88" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -9177,84 +9177,84 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S89" t="n">
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V89" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W89" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -9276,52 +9276,52 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_17.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_02.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -9333,27 +9333,27 @@
         <v>0.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S90" t="n">
         <v>12</v>
       </c>
       <c r="T90" t="n">
+        <v>8</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2</v>
+      </c>
+      <c r="V90" t="n">
+        <v>18</v>
+      </c>
+      <c r="W90" t="n">
         <v>5</v>
-      </c>
-      <c r="U90" t="n">
-        <v>9</v>
-      </c>
-      <c r="V90" t="n">
-        <v>12</v>
-      </c>
-      <c r="W90" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -9375,42 +9375,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9420,19 +9420,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V91" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -9474,47 +9474,47 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/key/key_50.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_45.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_38.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -9524,34 +9524,34 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S92" t="n">
         <v>14</v>
       </c>
       <c r="T92" t="n">
+        <v>16</v>
+      </c>
+      <c r="U92" t="n">
         <v>15</v>
       </c>
-      <c r="U92" t="n">
-        <v>13</v>
-      </c>
       <c r="V92" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="W92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9603,17 +9603,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -9623,18 +9623,18 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q93" t="n">
         <v>0.25</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="V93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -9677,17 +9677,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9697,43 +9697,43 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9743,13 +9743,13 @@
         <v>14</v>
       </c>
       <c r="U94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W94" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
@@ -9771,52 +9771,52 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9825,30 +9825,30 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S95" t="n">
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V95" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W95" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -9870,12 +9870,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9905,12 +9905,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -9931,23 +9931,23 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S96" t="n">
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V96" t="n">
         <v>4</v>
       </c>
       <c r="W96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -9969,42 +9969,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10014,19 +10014,19 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -10037,16 +10037,16 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W97" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98">
@@ -10068,32 +10068,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10103,22 +10103,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -10129,23 +10129,23 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S98" t="n">
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V98" t="n">
         <v>10</v>
       </c>
       <c r="W98" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10182,19 +10182,19 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -10202,22 +10202,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -10228,23 +10228,23 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S99" t="n">
         <v>8</v>
       </c>
       <c r="T99" t="n">
+        <v>9</v>
+      </c>
+      <c r="U99" t="n">
         <v>8</v>
-      </c>
-      <c r="U99" t="n">
-        <v>5</v>
       </c>
       <c r="V99" t="n">
         <v>14</v>
       </c>
       <c r="W99" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -10266,27 +10266,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_10.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U100" t="n">
         <v>10</v>
       </c>
       <c r="V100" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W100" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_49.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="P101" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q101" t="n">
         <v>0.4</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0.27</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -10439,10 +10439,10 @@
         <v>4</v>
       </c>
       <c r="V101" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10469,17 +10469,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -10514,18 +10514,18 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -10535,10 +10535,10 @@
         <v>4</v>
       </c>
       <c r="U102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V102" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W102" t="n">
         <v>8</v>
@@ -10563,32 +10563,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_13.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/key/key_30.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10598,49 +10598,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P103" t="n">
         <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S103" t="n">
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V103" t="n">
         <v>15</v>
       </c>
       <c r="W103" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_45.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -10677,17 +10677,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10707,19 +10707,19 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P104" t="n">
         <v>0.73</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -10730,16 +10730,16 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U104" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V104" t="n">
         <v>14</v>
       </c>
       <c r="W104" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -10761,47 +10761,47 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_20.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_46.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_17.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -10811,34 +10811,34 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q105" t="n">
         <v>0.53</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S105" t="n">
         <v>14</v>
       </c>
       <c r="T105" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_45.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -614,18 +614,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -703,28 +703,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0.31</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,7 +737,7 @@
         <v>7</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>11</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -816,14 +816,14 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q4" t="n">
         <v>0.31</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
         <v>16</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,10 +935,10 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
         <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,38 +1089,38 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>9</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,14 +1311,14 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1331,10 +1331,10 @@
         <v>10</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1406,18 +1406,18 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1430,10 +1430,10 @@
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,38 +1485,38 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1529,10 +1529,10 @@
         <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1604,18 +1604,18 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>0.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1631,7 +1631,7 @@
         <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,38 +1683,38 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1826,10 +1826,10 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,38 +1980,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2103,14 +2103,14 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="Q17" t="n">
         <v>0.31</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,7 +2123,7 @@
         <v>9</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2257,14 +2257,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_33.jpg</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>ball</t>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0.42</v>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2321,10 +2321,10 @@
         <v>5</v>
       </c>
       <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
         <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,18 +2396,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,10 +2420,10 @@
         <v>10</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2499,14 +2499,14 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2519,10 +2519,10 @@
         <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2594,18 +2594,18 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,10 +2618,10 @@
         <v>7</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,38 +2673,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2782,28 +2782,28 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0.33</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2816,7 +2816,7 @@
         <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W24" t="n">
         <v>5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2997,11 +2997,11 @@
         <v>0.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3017,7 +3017,7 @@
         <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3096,7 +3096,7 @@
         <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>18</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3188,18 +3188,18 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>0.25</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3212,7 +3212,7 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
         <v>11</v>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3287,18 +3287,18 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3311,10 +3311,10 @@
         <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,38 +3366,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3410,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/car/car_15.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3485,18 +3485,18 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P31" t="n">
         <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3512,7 +3512,7 @@
         <v>3</v>
       </c>
       <c r="W31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_45.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q32" t="n">
         <v>0.42</v>
@@ -3608,7 +3608,7 @@
         <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
         <v>16</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3668,33 +3668,33 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P33" t="n">
         <v>0.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3710,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3777,19 +3777,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,38 +3861,38 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>10</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3975,19 +3975,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P36" t="n">
         <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>15</v>
       </c>
       <c r="W36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4064,33 +4064,33 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
         <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4106,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4158,38 +4158,38 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -4202,10 +4202,10 @@
         <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,38 +4257,38 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,10 +4301,10 @@
         <v>11</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,38 +4356,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,10 +4400,10 @@
         <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4475,18 +4475,18 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>18</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4554,38 +4554,38 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4598,10 +4598,10 @@
         <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W42" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,22 +4653,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4677,14 +4677,14 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,10 +4697,10 @@
         <v>9</v>
       </c>
       <c r="V43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4796,10 +4796,10 @@
         <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4851,38 +4851,38 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,10 +4895,10 @@
         <v>5</v>
       </c>
       <c r="V45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4970,18 +4970,18 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P46" t="n">
         <v>0.64</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5049,17 +5049,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5069,18 +5069,18 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5093,10 +5093,10 @@
         <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5148,38 +5148,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,10 +5192,10 @@
         <v>7</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5370,14 +5370,14 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5390,10 +5390,10 @@
         <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5489,10 +5489,10 @@
         <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5544,38 +5544,38 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,10 +5588,10 @@
         <v>16</v>
       </c>
       <c r="V52" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="W52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5658,16 +5658,16 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0.26</v>
@@ -5687,7 +5687,7 @@
         <v>15</v>
       </c>
       <c r="V53" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="W53" t="n">
         <v>13</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5752,28 +5752,28 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
         <v>0.25</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W54" t="n">
         <v>11</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5856,16 +5856,16 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q55" t="n">
         <v>0.25</v>
@@ -5885,7 +5885,7 @@
         <v>7</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" t="n">
         <v>16</v>
@@ -5920,12 +5920,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5960,18 +5960,18 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5984,10 +5984,10 @@
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W56" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6063,14 +6063,14 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q57" t="n">
         <v>0.36</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -6083,7 +6083,7 @@
         <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W57" t="n">
         <v>16</v>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6162,14 +6162,14 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6182,10 +6182,10 @@
         <v>3</v>
       </c>
       <c r="V58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W58" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_45.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6237,22 +6237,22 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6261,14 +6261,14 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6281,10 +6281,10 @@
         <v>9</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6360,14 +6360,14 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6380,10 +6380,10 @@
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6440,17 +6440,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6462,11 +6462,11 @@
         <v>0.53</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6482,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6558,14 +6558,14 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,10 +6578,10 @@
         <v>4</v>
       </c>
       <c r="V62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6657,14 +6657,14 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -6677,10 +6677,10 @@
         <v>6</v>
       </c>
       <c r="V63" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6732,17 +6732,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,18 +6752,18 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6776,10 +6776,10 @@
         <v>5</v>
       </c>
       <c r="V64" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -6875,10 +6875,10 @@
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_45.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6940,28 +6940,28 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q66" t="n">
         <v>0.26</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,7 +6974,7 @@
         <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W66" t="n">
         <v>15</v>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,22 +7029,22 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7053,14 +7053,14 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>18</v>
       </c>
       <c r="V67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,17 +7128,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7148,18 +7148,18 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W68" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
         <v>9</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W70" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7449,10 +7449,10 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         <v>5</v>
       </c>
       <c r="V71" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7524,38 +7524,38 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7568,10 +7568,10 @@
         <v>10</v>
       </c>
       <c r="V72" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W72" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7638,16 +7638,16 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q73" t="n">
         <v>0.53</v>
@@ -7667,7 +7667,7 @@
         <v>3</v>
       </c>
       <c r="V73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W73" t="n">
         <v>15</v>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7746,14 +7746,14 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7766,10 +7766,10 @@
         <v>7</v>
       </c>
       <c r="V74" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7836,19 +7836,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7865,10 +7865,10 @@
         <v>6</v>
       </c>
       <c r="V75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W75" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,38 +7920,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7964,10 +7964,10 @@
         <v>8</v>
       </c>
       <c r="V76" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8024,17 +8024,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8046,11 +8046,11 @@
         <v>0.73</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -8066,7 +8066,7 @@
         <v>13</v>
       </c>
       <c r="W77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8162,10 +8162,10 @@
         <v>16</v>
       </c>
       <c r="V78" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,22 +8217,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8241,14 +8241,14 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>15</v>
       </c>
       <c r="V79" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="W79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
@@ -8360,7 +8360,7 @@
         <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
         <v>16</v>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/car/car_15.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8415,22 +8415,22 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8439,14 +8439,14 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,10 +8459,10 @@
         <v>7</v>
       </c>
       <c r="V81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W81" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/car/car_15.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8529,19 +8529,19 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -8558,10 +8558,10 @@
         <v>1</v>
       </c>
       <c r="V82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W82" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8613,38 +8613,38 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -8657,10 +8657,10 @@
         <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W83" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_45.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/car/car_15.jpg</t>
+          <t>stimuli/pencil/pencil_06.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8712,38 +8712,38 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -8756,10 +8756,10 @@
         <v>3</v>
       </c>
       <c r="V84" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W84" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/hand/hand_45.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8811,38 +8811,38 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -8855,10 +8855,10 @@
         <v>9</v>
       </c>
       <c r="V85" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="W85" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8930,18 +8930,18 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>0.75</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8957,7 +8957,7 @@
         <v>4</v>
       </c>
       <c r="W86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/car/car_15.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,17 +9009,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9029,18 +9029,18 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -9053,10 +9053,10 @@
         <v>10</v>
       </c>
       <c r="V87" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9108,38 +9108,38 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9152,10 +9152,10 @@
         <v>4</v>
       </c>
       <c r="V88" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9222,19 +9222,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -9251,10 +9251,10 @@
         <v>6</v>
       </c>
       <c r="V89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W89" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/lamp/lamp_32.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9306,22 +9306,22 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -9330,14 +9330,14 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -9350,10 +9350,10 @@
         <v>5</v>
       </c>
       <c r="V90" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W90" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/key/key_32.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9429,14 +9429,14 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9449,10 +9449,10 @@
         <v>11</v>
       </c>
       <c r="V91" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_32.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/key/key_32.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9504,22 +9504,22 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9528,14 +9528,14 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -9548,10 +9548,10 @@
         <v>16</v>
       </c>
       <c r="V92" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W92" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9603,22 +9603,22 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9627,14 +9627,14 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,10 +9647,10 @@
         <v>18</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W93" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9717,19 +9717,19 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -9746,10 +9746,10 @@
         <v>4</v>
       </c>
       <c r="V94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W94" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hand/hand_42.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9801,38 +9801,38 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -9845,10 +9845,10 @@
         <v>9</v>
       </c>
       <c r="V95" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9915,19 +9915,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -9944,10 +9944,10 @@
         <v>1</v>
       </c>
       <c r="V96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
+          <t>stimuli/guitar/guitar_28.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9999,38 +9999,38 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -10043,10 +10043,10 @@
         <v>5</v>
       </c>
       <c r="V97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_33.jpg</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>dog</t>
@@ -10098,14 +10098,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>right</t>
@@ -10113,19 +10113,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q98" t="n">
         <v>0.6899999999999999</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0.47</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -10142,10 +10142,10 @@
         <v>10</v>
       </c>
       <c r="V98" t="n">
+        <v>3</v>
+      </c>
+      <c r="W98" t="n">
         <v>6</v>
-      </c>
-      <c r="W98" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/pencil/pencil_20.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/glasses/glasses_19.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,38 +10197,38 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -10241,10 +10241,10 @@
         <v>3</v>
       </c>
       <c r="V99" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W99" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
@@ -10276,14 +10276,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>stimuli/key/key_33.jpg</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>bread</t>
@@ -10296,38 +10296,38 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P100" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q100" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0.47</v>
-      </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -10340,10 +10340,10 @@
         <v>7</v>
       </c>
       <c r="V100" t="n">
+        <v>2</v>
+      </c>
+      <c r="W100" t="n">
         <v>15</v>
-      </c>
-      <c r="W100" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,38 +10395,38 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10439,10 +10439,10 @@
         <v>6</v>
       </c>
       <c r="V101" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -10538,10 +10538,10 @@
         <v>8</v>
       </c>
       <c r="V102" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="W102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10608,19 +10608,19 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P103" t="n">
         <v>0.67</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>18</v>
       </c>
       <c r="W103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -10672,12 +10672,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
         <v>16</v>
       </c>
       <c r="V104" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P105" t="n">

--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_26.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>16</v>
@@ -668,12 +668,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -734,10 +734,10 @@
         <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
         <v>11</v>
@@ -762,17 +762,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,17 +782,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
         <v>16</v>
@@ -861,12 +861,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -929,10 +929,10 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>8</v>
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_36.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_01.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_26.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_36.jpg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_40.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
         <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
         <v>16</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
         <v>8</v>
@@ -1262,19 +1262,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_44.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_15.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_15.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>hand</t>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1328,13 +1328,13 @@
         <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
         <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
         <v>8</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
         <v>15</v>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>18</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
         <v>16</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2148,42 +2148,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_06.jpg</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_19.jpg</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_06.jpg</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2216,16 +2216,16 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
         <v>9</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
       <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="n">
         <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2315,13 +2315,13 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
         <v>8</v>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2414,16 +2414,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
         <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_04.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
+        <v>7</v>
+      </c>
+      <c r="V21" t="n">
         <v>3</v>
       </c>
-      <c r="V21" t="n">
-        <v>2</v>
-      </c>
       <c r="W21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
         <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,7 +2810,7 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
         <v>8</v>
@@ -2819,7 +2819,7 @@
         <v>18</v>
       </c>
       <c r="W24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2912,13 +2912,13 @@
         <v>8</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>16</v>
@@ -3017,7 +3017,7 @@
         <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>18</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
         <v>11</v>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_08.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_36.jpg</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3308,13 +3308,13 @@
         <v>14</v>
       </c>
       <c r="U29" t="n">
+        <v>10</v>
+      </c>
+      <c r="V29" t="n">
         <v>7</v>
       </c>
-      <c r="V29" t="n">
-        <v>3</v>
-      </c>
       <c r="W29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3404,13 +3404,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
         <v>16</v>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
         <v>15</v>
@@ -3534,17 +3534,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3554,17 +3554,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3602,13 +3602,13 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
         <v>16</v>
@@ -3633,42 +3633,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3800,16 +3800,16 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3902,13 +3902,13 @@
         <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
         <v>14</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
         <v>15</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4097,10 +4097,10 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
         <v>14</v>
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_06.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_06.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_40.jpg</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>16</v>
       </c>
       <c r="W38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>11</v>
@@ -4304,7 +4304,7 @@
         <v>15</v>
       </c>
       <c r="W39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4400,7 +4400,7 @@
         <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
         <v>15</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>18</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
         <v>15</v>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_19.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4549,17 +4549,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4595,13 +4595,13 @@
         <v>18</v>
       </c>
       <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
         <v>4</v>
       </c>
-      <c r="V42" t="n">
-        <v>10</v>
-      </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4643,17 +4643,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4691,13 +4691,13 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
         <v>16</v>
@@ -4722,17 +4722,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_06.jpg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_19.jpg</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
         <v>9</v>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
       <c r="V44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
         <v>15</v>
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_28.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_43.jpg</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_07.jpg</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>13</v>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4988,10 +4988,10 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V46" t="n">
         <v>8</v>
@@ -5019,19 +5019,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_07.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_04.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_26.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_20.jpg</t>
@@ -5039,17 +5039,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5087,13 +5087,13 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>7</v>
+      </c>
+      <c r="V47" t="n">
         <v>10</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" t="n">
-        <v>7</v>
       </c>
       <c r="W47" t="n">
         <v>16</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
         <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V49" t="n">
         <v>18</v>
       </c>
       <c r="W49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -5316,42 +5316,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_43.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_42.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_42.jpg</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U50" t="n">
         <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5486,13 +5486,13 @@
         <v>8</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V51" t="n">
         <v>18</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
         <v>16</v>
@@ -5591,7 +5591,7 @@
         <v>13</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W54" t="n">
         <v>11</v>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
         <v>16</v>
@@ -5910,19 +5910,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>stimuli/house/house_40.jpg</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_44.jpg</t>
-        </is>
-      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>stimuli/car/car_15.jpg</t>
@@ -5930,17 +5930,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
+        <v>9</v>
+      </c>
+      <c r="V56" t="n">
         <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>4</v>
       </c>
       <c r="W56" t="n">
         <v>11</v>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6029,17 +6029,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6077,13 +6077,13 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W57" t="n">
         <v>16</v>
@@ -6108,17 +6108,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6128,17 +6128,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6176,13 +6176,13 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W58" t="n">
         <v>11</v>
@@ -6207,42 +6207,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6275,16 +6275,16 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U59" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6374,13 +6374,13 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W60" t="n">
         <v>16</v>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6476,13 +6476,13 @@
         <v>8</v>
       </c>
       <c r="U61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V61" t="n">
         <v>15</v>
       </c>
       <c r="W61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6618,17 +6618,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
         <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6770,10 +6770,10 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V64" t="n">
         <v>15</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6974,7 +6974,7 @@
         <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W66" t="n">
         <v>15</v>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>18</v>
       </c>
       <c r="V67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W67" t="n">
         <v>15</v>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7169,10 +7169,10 @@
         <v>18</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
         <v>8</v>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7265,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W69" t="n">
         <v>15</v>
@@ -7296,14 +7296,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_06.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_19.jpg</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_42.jpg</t>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
+        <v>6</v>
+      </c>
+      <c r="U70" t="n">
         <v>9</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>8</v>
@@ -7395,42 +7395,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7463,16 +7463,16 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
         <v>13</v>
       </c>
       <c r="W72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W73" t="n">
         <v>15</v>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7760,10 +7760,10 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V74" t="n">
         <v>16</v>
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U76" t="n">
         <v>8</v>
       </c>
       <c r="V76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -7994,19 +7994,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_28.jpg</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_28.jpg</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_43.jpg</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>hand</t>
@@ -8014,17 +8014,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8060,13 +8060,13 @@
         <v>8</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V77" t="n">
         <v>13</v>
       </c>
       <c r="W77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,16 +8156,16 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
         <v>16</v>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8264,7 +8264,7 @@
         <v>18</v>
       </c>
       <c r="W79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W80" t="n">
         <v>16</v>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>14</v>
       </c>
       <c r="U81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W81" t="n">
         <v>11</v>
@@ -8484,17 +8484,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W82" t="n">
         <v>16</v>
@@ -8583,42 +8583,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_36.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_45.jpg</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_45.jpg</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8651,16 +8651,16 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V83" t="n">
         <v>8</v>
       </c>
       <c r="W83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8702,17 +8702,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8750,13 +8750,13 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U84" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W84" t="n">
         <v>16</v>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8796,17 +8796,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8849,16 +8849,16 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V85" t="n">
         <v>8</v>
       </c>
       <c r="W85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8890,17 +8890,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8948,16 +8948,16 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U86" t="n">
         <v>8</v>
       </c>
       <c r="V86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9050,13 +9050,13 @@
         <v>8</v>
       </c>
       <c r="U87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V87" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_08.jpg</t>
+          <t>stimuli/chair/chair_44.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_44.jpg</t>
+          <t>stimuli/ball/ball_36.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_36.jpg</t>
+          <t>stimuli/hammer/hammer_01.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V89" t="n">
         <v>15</v>
       </c>
       <c r="W89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_26.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_42.jpg</t>
+          <t>stimuli/bread/bread_36.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V90" t="n">
         <v>14</v>
       </c>
       <c r="W90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_42.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9385,17 +9385,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/jacket/jacket_08.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_40.jpg</t>
+          <t>stimuli/flower/flower_26.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
         <v>11</v>
       </c>
       <c r="V91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W91" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_36.jpg</t>
+          <t>stimuli/house/house_40.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9548,7 +9548,7 @@
         <v>16</v>
       </c>
       <c r="V92" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W92" t="n">
         <v>15</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>18</v>
       </c>
       <c r="V93" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W93" t="n">
         <v>15</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9743,10 +9743,10 @@
         <v>18</v>
       </c>
       <c r="U94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W94" t="n">
         <v>16</v>
@@ -9771,12 +9771,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_07.jpg</t>
+          <t>stimuli/ball/ball_19.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/flower/flower_06.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9839,10 +9839,10 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V95" t="n">
         <v>8</v>
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_06.jpg</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_19.jpg</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,17 +9890,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
+        <v>6</v>
+      </c>
+      <c r="U96" t="n">
         <v>9</v>
       </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
       <c r="V96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W96" t="n">
         <v>16</v>
@@ -9969,17 +9969,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W97" t="n">
         <v>13</v>
@@ -10068,42 +10068,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_07.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_04.jpg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_26.jpg</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_06.jpg</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10136,16 +10136,16 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
+        <v>2</v>
+      </c>
+      <c r="U98" t="n">
+        <v>4</v>
+      </c>
+      <c r="V98" t="n">
+        <v>7</v>
+      </c>
+      <c r="W98" t="n">
         <v>5</v>
-      </c>
-      <c r="U98" t="n">
-        <v>10</v>
-      </c>
-      <c r="V98" t="n">
-        <v>3</v>
-      </c>
-      <c r="W98" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
+          <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/hammer/hammer_04.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10235,10 +10235,10 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V99" t="n">
         <v>16</v>
@@ -10266,19 +10266,19 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_04.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_03.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
-        </is>
-      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>stimuli/key/key_33.jpg</t>
@@ -10286,17 +10286,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10334,13 +10334,13 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
+        <v>7</v>
+      </c>
+      <c r="U100" t="n">
+        <v>10</v>
+      </c>
+      <c r="V100" t="n">
         <v>3</v>
-      </c>
-      <c r="U100" t="n">
-        <v>7</v>
-      </c>
-      <c r="V100" t="n">
-        <v>2</v>
       </c>
       <c r="W100" t="n">
         <v>15</v>
@@ -10365,42 +10365,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_19.jpg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_07.jpg</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_03.jpg</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
         <v>4</v>
-      </c>
-      <c r="W101" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_43.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10474,17 +10474,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_19.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U102" t="n">
         <v>8</v>
       </c>
       <c r="V102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -10568,19 +10568,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_19.jpg</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_19.jpg</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_43.jpg</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>hand</t>
@@ -10588,17 +10588,17 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10634,13 +10634,13 @@
         <v>8</v>
       </c>
       <c r="U103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V103" t="n">
         <v>18</v>
       </c>
       <c r="W103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -10662,42 +10662,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_20.jpg</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_20.jpg</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_43.jpg</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_04.jpg</t>
+          <t>stimuli/jacket/jacket_03.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,16 +10730,16 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U104" t="n">
         <v>16</v>
       </c>
       <c r="V104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W104" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_43.jpg</t>
+          <t>stimuli/bicycle/bicycle_44.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>18</v>
       </c>
       <c r="W105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
